--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_02/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_02/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>61.01</v>
+        <v>60.4</v>
       </c>
       <c r="D2" t="n">
-        <v>20.92</v>
+        <v>19.89</v>
       </c>
       <c r="E2" t="n">
-        <v>34.3</v>
+        <v>32.92</v>
       </c>
       <c r="F2" t="n">
-        <v>36.1</v>
+        <v>37.77</v>
       </c>
       <c r="G2" t="n">
-        <v>42.92</v>
+        <v>42.9</v>
       </c>
       <c r="H2" t="n">
-        <v>55.14</v>
+        <v>54.99</v>
       </c>
       <c r="I2" t="n">
-        <v>79.12</v>
+        <v>76.72</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>63.9</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>46.36</v>
+        <v>38.59</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02</v>
+        <v>0.77</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04</v>
+        <v>1.99</v>
       </c>
       <c r="F3" t="n">
-        <v>46.34</v>
+        <v>33.62</v>
       </c>
       <c r="G3" t="n">
-        <v>46.36</v>
+        <v>38.58</v>
       </c>
       <c r="H3" t="n">
-        <v>46.36</v>
+        <v>38.6</v>
       </c>
       <c r="I3" t="n">
-        <v>46.37</v>
+        <v>38.62</v>
       </c>
       <c r="J3" t="n">
-        <v>46.46</v>
+        <v>40.02</v>
       </c>
       <c r="K3" t="n">
-        <v>0.12</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.02</v>
+        <v>7.92</v>
       </c>
       <c r="D4" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="E4" t="n">
-        <v>29.45</v>
+        <v>29.38</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="G4" t="n">
-        <v>5.33</v>
+        <v>6.14</v>
       </c>
       <c r="H4" t="n">
-        <v>5.93</v>
+        <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>8.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>11.64</v>
+        <v>13.1</v>
       </c>
       <c r="K4" t="n">
-        <v>6.64</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>87.62</v>
+        <v>64.33</v>
       </c>
       <c r="D5" t="n">
-        <v>44.13</v>
+        <v>15.02</v>
       </c>
       <c r="E5" t="n">
-        <v>50.37</v>
+        <v>23.35</v>
       </c>
       <c r="F5" t="n">
-        <v>47.7</v>
+        <v>42.82</v>
       </c>
       <c r="G5" t="n">
-        <v>58.15</v>
+        <v>53.68</v>
       </c>
       <c r="H5" t="n">
-        <v>67.3</v>
+        <v>54.91</v>
       </c>
       <c r="I5" t="n">
-        <v>92.3</v>
+        <v>71.55</v>
       </c>
       <c r="J5" t="n">
-        <v>190.53</v>
+        <v>100.32</v>
       </c>
       <c r="K5" t="n">
-        <v>142.83</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.94</v>
+        <v>4.49</v>
       </c>
       <c r="D6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
-        <v>21.48</v>
+        <v>13.47</v>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>4.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.95</v>
+        <v>4.76</v>
       </c>
       <c r="I6" t="n">
-        <v>3.01</v>
+        <v>4.88</v>
       </c>
       <c r="J6" t="n">
-        <v>4.61</v>
+        <v>4.98</v>
       </c>
       <c r="K6" t="n">
-        <v>2.59</v>
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>
